--- a/docs/research/2026-07-08-ERP-MES-연계-데이터-제공요청서.xlsx
+++ b/docs/research/2026-07-08-ERP-MES-연계-데이터-제공요청서.xlsx
@@ -98,7 +98,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -120,11 +120,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -162,6 +206,8 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,6 +605,12 @@
           <t>본 시트는 ERP(UNIERP)에서 연계로 수신하는 데이터입니다. 각 항목의 ①테이블 정의(컬럼·키·타입)와 ②샘플 데이터를 요청드립니다. ERP가 아닌 현행 자료(설비·도구·공정 등)는 「3. MES 구축용 현행 자료 요청」 시트를 참조 바랍니다.</t>
         </is>
       </c>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="14" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -990,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1009,16 +1061,19 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>omf-MES ↔ ERP(UNIERP) 연계   |   작성: CREFLE OMF 팀 · 2026-07-08</t>
+          <t>omf-MES ↔ ERP(UNIERP) 연계   |   작성: CREFLE OMF 팀 · 2026-07-08 (갱신 2026-07-10)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>연계 구현 및 라벨 설계를 위해 아래 항목에 대한 제공·확인·회신을 요청드립니다.</t>
-        </is>
-      </c>
+          <t>연계 구현·라벨 설계 및 현장 인프라 준비를 위해 아래 항목에 대한 제공·확인·회신을 요청드립니다.</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="14" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1119,6 +1174,46 @@
       <c r="D9" s="8" t="inlineStr">
         <is>
           <t>송신(MES→ERP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>MES 서버·백업 NAS 설치 협의 (신규 07-10)</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>MES 서버 2대(이중화 구성)와 백업용 NAS를 공장 내부에 설치합니다. 설치 공간·전원(UPS)·네트워크 협의와 함께, 백업 NAS의 설치 위치를 선택해 회신 부탁드립니다. — ① 서버와 다른 건물·공간에 설치(권장 — 화재 등 국지 재해에서도 백업 보존) ② 주기적 외장 매체 복제·외부 보관 병행 ③ 유지보수 시점 외부 복제 ④ 서버와 동일 공간(이 경우 국지 재해 시 원본·백업 동시 소실 위험 수용).</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>인프라·백업</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>관리자 알림 채널 운영 방식 확인 (신규 07-10)</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>운영 중 인터넷 사용이 보장되지 않는 사내망 환경이므로, 정본 알림은 시스템 내 채널(관리 대시보드·알림센터·현장 단말 표시, 지정 담당자 수신)로 제공됩니다. 카카오톡/Zalo 메신저 알림은 인터넷이 가능한 시점에만 동작하는 보조 채널로 운영됩니다. 이 운영 방식에 대한 확인과, 알림 수신 담당자 지정을 요청드립니다.</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>알림 운영</t>
         </is>
       </c>
     </row>
@@ -1170,6 +1265,12 @@
           <t>아래는 ①ERP 연계 대상이 아니라 현재 엑셀·대장·종이로 관리되는 마스터(MES 초기 등록·이행용)와, ②기능 개발 검토를 위한 샘플 문서입니다. 가능한 원본 파일(양식 포함)의 제공을 요청드립니다.</t>
         </is>
       </c>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="13" t="n"/>
+      <c r="G3" s="14" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
